--- a/output/full_scan/batch_seq1_2026-10-20.xlsx
+++ b/output/full_scan/batch_seq1_2026-10-20.xlsx
@@ -428,11 +428,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1569</v>
+        <v>1216</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>989.1665131375896</v>
+        <v>1020.221617034384</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>79.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>73.07687346542889</v>
+        <v>61.91097291293978</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>67.42185872979019</v>
+        <v>25.05295318643389</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.5692271675803329</v>
+        <v>0.8221617034383615</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.4760332909204132</v>
+        <v>0.5772630284835235</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1101</v>
+        <v>1569</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>955.8289236252812</v>
+        <v>989.1665131375896</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>26.8</v>
+        <v>79.7</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>59.73706299117817</v>
+        <v>73.07687346542889</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>49.41575363131652</v>
+        <v>67.42185872979019</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.6646794697458974</v>
+        <v>0.5692271675803329</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1239266871358082</v>
+        <v>0.4760332909204132</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>888.2001713108889</v>
+        <v>955.8289236252812</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>37.9</v>
+        <v>26.8</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>70.43686505923509</v>
+        <v>59.73706299117817</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>33.65678741166246</v>
+        <v>49.41575363131652</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.9708040645937428</v>
+        <v>0.6646794697458974</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1883307258351052</v>
+        <v>0.1239266871358082</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1103</v>
+        <v>1476</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>752.2077088709589</v>
+        <v>910.8358423026584</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13.35</v>
+        <v>325.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>57.82198542648756</v>
+        <v>67.52792743205669</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>36.57235792468732</v>
+        <v>38.73028995366455</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.7144532202201925</v>
+        <v>0.8785438924231327</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.0277777884491764</v>
+        <v>5.433567881277821</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1582</v>
+        <v>1477</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>340.6758659534461</v>
+        <v>903.4308323119682</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>70.09999999999999</v>
+        <v>207.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>43.82086328382843</v>
+        <v>61.80555724004963</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>12.48092038901887</v>
+        <v>32.1575929705031</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.7697370310927264</v>
+        <v>0.4923205399424539</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.0022316927880972</v>
+        <v>1.534119510141376</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>325.2386740696962</v>
+        <v>888.2001713108889</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>26.7</v>
+        <v>37.9</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>46.02502183195897</v>
+        <v>70.43686505923509</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>17.09986631716626</v>
+        <v>33.65678741166246</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.7521287039239333</v>
+        <v>0.9708040645937428</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,48 +835,48 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.0130818609168732</v>
+        <v>0.1883307258351052</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1529</v>
+        <v>1516</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>295.4958780964449</v>
+        <v>854</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>14.8</v>
+        <v>18.55</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>36.81753214686979</v>
+        <v>72.81261402280258</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>20.41607546936956</v>
+        <v>16.81551481074131</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.438772575993671</v>
+        <v>5.434070040980664</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.0372124594127045</v>
+        <v>0.536008780733787</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1471</v>
+        <v>1434</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>240.0360401552846</v>
+        <v>792.469376812838</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>9.050000000000001</v>
+        <v>19.7</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>33.76680864485071</v>
+        <v>60.0489994845869</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>14.97536217144734</v>
+        <v>38.89678638213618</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.4973342669762202</v>
+        <v>0.6777158175125163</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>1</v>
@@ -941,11 +941,6583 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
+        <v>0.1352026248943849</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>1416</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>廣豐</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>791.9788880437544</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>71.37170892414672</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>40.68625216374948</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0.7596675761697222</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0.1276260697538878</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>1310</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>台苯</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>767.6222605620835</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>55.49051920009403</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>47.4802358366445</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0.5447629675376517</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>0.008798242402263101</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>1323</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>永裕</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>761.2206861866238</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>58.82689128959859</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>25.1263961213128</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>1.296165237844186</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>0.0291549260448651</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>1321</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>大洋</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>760.6741931520163</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>67.59236295599848</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>27.22320747896992</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1.067419315201634</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>0.3400610349937494</v>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>嘉泥</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>752.2077088709589</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>57.82198542648756</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>36.57235792468732</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.7144532202201925</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>0.0277777884491764</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>1558</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>伸興</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>746.5298877677816</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>62.45361630842559</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>25.26478974662121</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.6579002809643397</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>0.0579617457946977</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>1445</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>大宇</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>744.654926168626</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>52.60719965017379</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>29.85795442184425</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>1.716184503516109</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>0.0161078664739867</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>1236</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>宏亞</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>733.2772733878445</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>56.34352181112744</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>18.18552450695214</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>4.984646001140183</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>0.0464365410440848</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>1319</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>東陽</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>696.6547134402497</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>54.95889846705099</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>26.36107944290368</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0.3575551989872447</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>0.3026195919782377</v>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>1303</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>695.3584624893426</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>57.42072632661531</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>44.56353090372509</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>1.13700185604751</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>-0.3248721024633383</v>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>1315</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>達新</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>690.4368736727215</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>51.7675906627879</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>52.49413671390441</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>1.029064473490968</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>-0.0725330785751932</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>1312</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>國喬</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>657.9778528167075</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>48.04981074220501</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>45.31301747037491</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0.7841681984293413</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>-0.0693257585722956</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>1409</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>新纖</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>654.2614939846752</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>48.74746266882596</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>25.18560960846325</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0.4134312824777206</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>-0.0266749629844884</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>1463</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>強盛新</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>649.1232519166492</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>59.22251411409388</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>15.65738996981431</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0.6116034962660485</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>0.0420325084608434</v>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>1440</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>南紡</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>644.014376811829</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>50.71240465250449</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>22.7374462953766</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0.3974722491273393</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>0.0215707849079939</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>1326</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>台化</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>643.7823242413607</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>52.02547457577016</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>35.83102956509441</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0.6892226516309566</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>-0.0300106787767457</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>1528</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>恩德</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>639.4025026779408</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>54.94236852016</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>31.96037863693552</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0.9129189117233506</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>-0.1730371156018981</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>雋揚</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>639.3361971432067</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>28.85</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>51.83763375162925</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>15.15413697415852</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0.9943221568439734</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>0.4823297914134014</v>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>1532</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>勤美</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>631.6176075931423</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>43.63990986404784</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>21.427505621409</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0.5017665506233269</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>0.005008499124797</v>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>巧新</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>623.8483355278245</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>55.04187074052989</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>42.78964956203853</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0.4548672483524395</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>-0.3026770420465343</v>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>1402</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>遠東新</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>622.8433027892058</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>50.00506182341911</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>20.27488222097926</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0.7251288845279885</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>0.0670564822871033</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>1301</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>台塑</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>616.0972645235429</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>53.95024059107218</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>40.2018029738704</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0.7912809352310324</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>0.2511910372379935</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>1524</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>耿鼎</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>615.7069926648278</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>58.24370955261816</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>30.16401773432874</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0.670699266482771</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>0.1437796535349557</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>1437</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>勤益控</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>610.889702705526</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>48.23914277329932</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>18.61690221074502</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>2.582876682259149</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>-0.0642288483886236</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>1455</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>集盛</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>608.61116051459</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>48.05329749316434</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>35.38692679198174</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.4414635528649015</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>-0.0221116611687884</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>1560</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>608.5045245595429</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>858</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>43.18532023590097</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>36.3024564762497</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0.885564810143792</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>-25.35342575654776</v>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>1526</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>日馳</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>603.236342213285</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>60.00185902588534</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>18.50248834803172</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>5.760954276057666</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>0.1933844139177367</v>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>1441</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>大東</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>600.6572524773029</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>64.54087133973977</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>27.57585031406133</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0.257522151229515</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>0.0021603902613333</v>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>1314</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>中石化</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>595.7288904624988</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>48.71054474988076</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>38.31613284403922</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0.4045434713634696</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>-0.0484043687346763</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>1256</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>鮮活果汁-KY</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>594.5726198701377</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>47.98905143381317</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>9.114997643030676</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0.7537594803761659</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>0.4238450877569391</v>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>1325</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>恆大</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>586.0285070576011</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>50.55650469513324</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>32.40012064332149</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0.3411981396377831</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>-0.009541117378249</v>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>1459</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>聯發</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>573.8146431510676</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>57.59172213339312</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>64.74035499837588</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>0.2646726976283137</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>-0.1114333936720283</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>1513</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>中興電</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>560.099985106757</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>39.68872423622432</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>10.23268953380947</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0.5326246840088706</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>-0.6918986770602173</v>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, dealer_buy_3d, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>南染</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>556.008856209877</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>36.96518337561599</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>7.044375432035233</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0.8528292065707032</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>-0.0169455169068163</v>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>1313</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>539.9621993109168</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>47.70304308646296</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>32.757962740182</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>0.9720217982543884</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>-0.0213935467136152</v>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>1210</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>大成</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>539.8622940644149</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>39.76209179934561</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>24.28208260149358</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>1.452454445286758</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>0.0319215715599506</v>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>1232</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>大統益</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>534.2433412713551</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>48.2600521624483</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>17.78881652942597</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>1.204632079823262</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>0.2081890394058692</v>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>1512</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>瑞利</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>533.1223455346915</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>51.17445225067481</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>20.29617812301753</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>1.703296916418487</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>0.0248744216248059</v>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>1309</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>台達化</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>528.3991810772645</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>46.60069080291426</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>37.9247948600849</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>0.912134034645578</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>-0.027634703621617</v>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>1213</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>大飲</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>515.8462512352583</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>51.27609775394984</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>9.855817552778644</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>0.3365255526716191</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>-0.2930716609263269</v>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>1456</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>513.6436601482546</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>47.54455013724404</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>23.51046337021057</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0.7577327860958888</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>-0.0306201060782821</v>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>1419</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>新紡</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>510.0367559500561</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>36.75034989577111</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>13.37970188815866</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>2.477315584919569</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>-0.2554758642178812</v>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>1504</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>502.9191029065856</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>43.23050218246146</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>14.82188844723727</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0.6037667808517143</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>-0.1765673395219596</v>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>1470</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>大統新創</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>496.2293578512716</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>51.89389556234249</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>12.9358797882858</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>0.4731289467157601</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>-0.4562063223663272</v>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>1457</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>宜進</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>491.2966097457317</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>51.83157208360092</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>15.46394883902916</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>1.000862020730462</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>0.0243572737887294</v>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>1305</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>華夏</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>490.8975047362283</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>51.52047935674172</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>33.00457724975323</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>0.5275855389269165</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>0.0132922520146748</v>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>1225</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>福懋油</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>489.971734865255</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>44.8805520115583</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>28.81211799677621</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>1.041449459231996</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>0.0537487377575938</v>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>1465</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>偉全</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>488.3626350104952</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>48.1214718163856</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>18.98656321652276</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>2.073115302079342</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>0.0350114273502908</v>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>1535</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>中宇</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>483.981159456563</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>45.65</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>47.90760016044268</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>20.01378901738921</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>0.8551509049756629</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>0.0321717321065924</v>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>1443</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>立益</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>480.0872480538318</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>41.4980383514819</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>14.11020780439716</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>0.4456759490606655</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>-0.0225575267994604</v>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>1451</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>年興</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>479.7871825106427</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>43.05829143633579</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>14.23482348321759</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>0.6797688098092378</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>0.0127180854617449</v>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>1304</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>台聚</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>478.2157604803979</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>51.1677897994248</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>38.54744551380984</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>0.6415471143574141</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>0.0153349211970976</v>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>1423</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>477.8079461925542</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>51.23606258072473</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>9.125850113180102</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>0.5687338427885571</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>0.1360983899564535</v>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>1418</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>東華</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>472.6856607014927</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>45.28084366847502</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>40.10712135825781</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>0.6043663471778488</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>-0.0467635548795593</v>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>1447</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>力鵬</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>447.653383704676</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>44.78985249235483</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>25.08391706652918</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>0.9770376628918006</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>0.009199922006709899</v>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>1413</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>宏洲</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>441.684935910324</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>49.45221646931726</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>9.310169156710138</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>0.2570165887401524</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>0.0169552390735266</v>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>1522</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>堤維西</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>438.3072693904702</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>51.42053673937368</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>14.36849294091081</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>0.6046617962094124</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>0.1483468548843392</v>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>1539</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>巨庭</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>432.1332016953587</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>37.8288364433655</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>30.39496625886042</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>1.431505471866325</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>-0.0134443694396733</v>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>1514</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>亞力</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>427.5088690123594</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>40.46624779612699</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>12.56925907316694</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0.858639136772783</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>-0.3745896965899214</v>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>1308</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>亞聚</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>425.576354196849</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>44.61052517928371</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>35.93398233314102</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>0.7366166900680698</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>-0.0464208325311978</v>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>東泥</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>420.0484463075477</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>32.3444057291015</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>43.46618220979113</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>0.5109884495479881</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>0.0303179998343602</v>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>1339</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>昭輝</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>419.1146225128819</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>41.65</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>37.11037289420084</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>27.94537296639396</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>0.5658191170830285</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>-0.008474061073054101</v>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>1473</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>417.7125978062469</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>27.07158218197306</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>48.07400177996441</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>1.181414701640352</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>-0.010606900898739</v>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>1231</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>聯華食</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>413.1037410513695</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>22.74956666324532</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>30.95818016961559</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>1.825020293855899</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>-0.2417200083970206</v>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>1460</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>宏遠</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>412.7068390795841</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>33.55001809765295</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>28.22190876911285</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>0.837353751398778</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>0.009602437572133599</v>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>1229</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>聯華</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>405.9978115291901</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>44.15807295890954</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>19.48221482624004</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>0.8753044546226715</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>0.1042604304620886</v>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>1446</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>宏和</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>402.3766765758915</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>46.68895844239164</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>12.54397115444727</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>0.4827469556647267</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>0.0169574625902573</v>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>1467</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>南緯</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>399.9439648751147</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>43.39552262024097</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>17.06891550060686</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>0.6416730091342843</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>-0.000663052299837</v>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>1316</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>上曜</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>398.8237146697303</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>43.46164289511121</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>15.56817363043506</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>0.5490420861363535</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>-0.0055889027908504</v>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>1417</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>嘉裕</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>397.1846563698936</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>45.21207950673463</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>13.98636103917028</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>0.4408112454641589</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>0.0073799598553088</v>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>1452</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>宏益</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>392.6795945534</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>53.61638996047007</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>15.79833718055473</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>1.976377919705074</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>0.0531563678904676</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>1442</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>名軒</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>391.2051370582448</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>33.59577290342328</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>30.98851945172836</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.3822220050992777</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>-0.0009612261123063</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>1464</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>得力</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>384.0934625524284</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>36.85773933229054</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>24.11983206992598</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0.7143793674457454</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>0.0041007350187896</v>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>廣隆</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>383.9714835387758</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>40.78800810575732</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>22.31680188610709</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0.7532412047915606</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>0.2461723891532909</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>1444</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>力麗</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>382.0999010583189</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>43.40718180405463</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>23.59104647491354</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0.8888866854345117</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>0.0035228069358219</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>1233</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>天仁</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>381.8040317042216</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>44.66300574689007</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>12.0851722129048</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>1.184369258911746</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>0.0065980020451622</v>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>1515</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>力山</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>381.1312147958689</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>38.71382137624726</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>6.973942261933113</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.7810959897811657</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>0.0473623451391702</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>1568</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>倉佑</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>380.2068360622686</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>38.25111970670642</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>21.5347226554474</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>0.6185204515933589</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>-0.3465645232918539</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>1220</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>台榮</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>379.3855929617428</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>44.11379777835922</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>17.59182007806616</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>0.8990194595958372</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>0.0048384469749435</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>1203</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>味王</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>377.6224449980127</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>44.42128577665233</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>9.021823094770062</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>1.95395013715578</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>0.0291327507917125</v>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>幸福</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>377.5225478456819</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>32.80011090969846</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>36.1291004223964</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0.4964899655819519</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>0.0203332800834338</v>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>1453</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>大將</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>373.6605527714661</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>47.1133307006149</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>17.98020605381984</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>1.083641235345793</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>0.0127174329633541</v>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>1432</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>大魯閣</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>370.6545192859463</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>36.44425016187291</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>18.18372710329427</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>1.09599370798907</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>-0.0030141009048432</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>1472</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>三洋實業</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>369.676332585309</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>52.35193166613842</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>6.979415000699902</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>0.5473430097815957</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>-0.0986618078094938</v>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>信大</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>367.4252931063678</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>31.97356622112454</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>37.2070528240887</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>0.9970839169374008</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>-0.0122404201525323</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>1521</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>大億</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>366.8704573589741</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>44.42713871238291</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>24.8092338453459</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>0.3439824239081409</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>-0.0503827874557502</v>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>1307</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>三芳</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>359.8852690635801</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>45.1715165083999</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>11.94740702972997</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>1.698360111593033</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>-0.0213263650200982</v>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>1474</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>弘裕</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>359.3948050323944</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>47.06193779772541</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>12.98675316178134</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0.4084511560938096</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>-0.0015848911124619</v>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>1506</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>正道</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>356.2035051249306</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>38.60922812411462</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>19.43412122887184</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>0.3808085554036054</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>0.0124416604182377</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>1342</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>八貫</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>354.7650487059884</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>35.57226061992921</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>16.23158903127143</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>1.156093950642095</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>-0.1215869277419043</v>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>1324</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>351.1738960649345</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>42.83953365827707</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>20.04706459669168</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0.4381337724981399</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>0.0001575998035268</v>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>1414</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>東和</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>344.9858850114944</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>51.78737607214119</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>19.09602189525497</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.5079465959419883</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>0.0892221812606898</v>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>1218</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>泰山</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>342.3368565192933</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>46.70729014594899</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>6.922016969432795</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0.9322940698348982</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>-0.000606845117267</v>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>1582</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>信錦</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>340.6758659534461</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>43.82086328382843</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>12.48092038901887</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>0.7697370310927264</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>-0.0022316927880972</v>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>1454</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>台富</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>338.4836038752578</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>45.57654730974941</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>24.12623476274888</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.9626570782228532</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>0.0123370154888407</v>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>1503</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>士電</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>337.4717933226864</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>40.79082495811744</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>10.6641923325327</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>1.264427116404662</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>-0.3809691414556139</v>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>1341</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>富林-KY</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>333.8417314239089</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>51.58381157826333</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>7.427545859265827</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>1.398525975193241</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>1.278424346182279</v>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>1201</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>味全</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>331.4465451703953</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>41.51620084977181</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>41.44783133117142</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.3004083883746691</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>0.0250226014967191</v>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>1517</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>利奇</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>330.2076831393086</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>42.68765359516602</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>22.99050633052596</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>0.5756903585012482</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>0.0261668535092463</v>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>1536</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>和大</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>328.1789105402099</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>31.17961095386964</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>20.36360116303231</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0.6069180380738537</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>-0.1168875563714175</v>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>環泥</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>325.2386740696962</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>46.02502183195897</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>17.09986631716626</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>0.7521287039239333</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>0.0130818609168732</v>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>1527</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>鑽全</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>323.1602788861745</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>42.94488697870278</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>9.20383070580057</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>0.4520717859798487</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>-0.0192055311336872</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>1338</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>廣華-KY</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>321.8987832762416</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>42.78752090385278</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>27.79127618273606</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>0.5020901926702591</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>-0.0597070118887137</v>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>1215</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>319.4634952997473</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>44.88691255364791</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>14.32019838076395</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.8844339465414761</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>0.2021469803253847</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>1219</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>福壽</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>317.7937999390315</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>39.65732332951707</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>14.10965548070362</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>1.129932105828058</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>-0.0211816206692019</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>1475</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>業旺</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>317.6460077320585</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>37.98013065131641</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>16.79201667264033</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>1.284099384796052</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-0.0434933025609628</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>愛之味</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>309.6714854098038</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>39.25334128559542</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>17.29473499646009</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.9658402034488562</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-0.0063132477656911</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>1340</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>勝悅-KY</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>303.9247703078383</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>40.07346654650636</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>11.53886512946706</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.9966787271546526</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>-0.0153186282518359</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>1227</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>佳格</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>299.5817335951104</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>40.42221092101729</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>17.74043083441468</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>1.214410353578708</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>0.0407818125356572</v>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>1525</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>江申</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>296.8000499488688</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>48.67234759411186</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>8.64148203261926</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>1.12085169243308</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>0.2428401011059106</v>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>1529</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>樂事綠能</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>295.4958780964449</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>36.81753214686979</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>20.41607546936956</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>0.438772575993671</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>-0.0372124594127045</v>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>1436</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>華友聯</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>268.1481890251365</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>38.71240335902286</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>12.02891576034368</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>0.4548608288976647</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>0.0476402772142253</v>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>1438</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>三地開發</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>267.1504135353125</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>48.41643078822597</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>7.067712508778388</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>0.4082211197732104</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>0.028007640351121</v>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>1468</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>266.8897929158608</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>46.33059022392437</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>8.737081851431578</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>0.5747189685384163</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>-0.0119089659568238</v>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>1466</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>聚隆</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>252.6288132271039</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>45.28306404460011</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>17.66845044399012</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>1.210168526315764</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>0.0604823933593734</v>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>1530</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>亞崴</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>251.9229125739507</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>43.93871825455085</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>19.31638753383082</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.5259209953662221</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>0.0435098101684598</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>1531</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>高林股</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>246.052872742487</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>43.88684967900341</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>17.45555848106914</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.7336617115419451</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>0.0366792545509514</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>1538</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>正峰</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>242.5974056459775</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>38.74514950811741</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>16.47191021337714</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-0.9050448044684546</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>1471</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>首利</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>240.0360401552846</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>33.76680864485071</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>14.97536217144734</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.4973342669762202</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
         <v>-0.0242427970115822</v>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O128" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>1540</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>喬福</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>219.2810778701137</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>37.48177379927277</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>11.4048582777943</v>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>0.4042816035675008</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" s="2" t="n">
+        <v>-0.0310868497776542</v>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>1519</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>218.4938175426313</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>631</v>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>36.04606476000552</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>12.03778676364691</v>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>0.7419685795334638</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N130" s="2" t="n">
+        <v>-6.014664775483439</v>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>1541</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>錩泰</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>216.6912948848531</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>49.57932210779306</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>11.3139596992066</v>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>1.323238052320387</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N131" s="2" t="n">
+        <v>0.1095198971148381</v>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>1533</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>車王電</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>214.2365867149606</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>26.80261440526982</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>14.37045051001508</v>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>0.653040617365598</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N132" s="2" t="n">
+        <v>-0.1021234870455172</v>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>1435</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>中福</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>73.41821407083239</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>49.27463198177755</v>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>6.493494161004552</v>
+      </c>
+      <c r="J133" s="2" t="n">
+        <v>0.4609680595346856</v>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N133" s="2" t="n">
+        <v>0.1533132080367358</v>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
